--- a/prompt/taqueria-ibarra-google-sheets-workbook.xlsx
+++ b/prompt/taqueria-ibarra-google-sheets-workbook.xlsx
@@ -2936,7 +2936,7 @@
         <v>America/Chicago</v>
       </c>
       <c r="W2" t="str">
-        <v>{"mon":[{"open":"11:00","close":"21:00","label":"Carryout"}],"tue":[{"open":"11:00","close":"21:30","label":"Carryout"}],"wed":[{"open":"11:00","close":"21:30","label":"Carryout"}],"thu":[{"open":"11:00","close":"21:30","label":"Carryout"}],"fri":[{"open":"11:00","close":"21:30","label":"Carryout"}],"sat":[{"open":"11:00","close":"21:30","label":"Carryout"}],"sun":[]}</v>
+        <v>{"mon":[{"open":"11:00","close":"21:00","label":"Carryout and delivery"}],"tue":[{"open":"11:00","close":"21:30","label":"Carryout and delivery"}],"wed":[{"open":"11:00","close":"21:30","label":"Carryout and delivery"}],"thu":[{"open":"11:00","close":"21:30","label":"Carryout and delivery"}],"fri":[{"open":"11:00","close":"21:30","label":"Carryout and delivery"}],"sat":[{"open":"11:00","close":"21:30","label":"Carryout and delivery"}],"sun":[]}</v>
       </c>
     </row>
   </sheetData>
